--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-documento-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-documento-urgencia.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/documento-urgencia</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/documento-urgencia</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -271,7 +271,7 @@
 </t>
   </si>
   <si>
-    <t>A reference to a document</t>
+    <t>Referencia al documento clínico de urgencia (PDF)</t>
   </si>
   <si>
     <t>A reference to a document of any kind for any purpose. Provides metadata about the document so that the document can be discovered and managed. The scope of a document is any seralized object with a mime-type, so includes formal patient centric documents (CDA), cliical notes, scanned paper, and non-patient specific documents like policy text.</t>
@@ -628,7 +628,7 @@
     <t>DocumentReference.masterIdentifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>Sistema de identificadores de documentos del establecimiento</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -655,7 +655,7 @@
     <t>DocumentReference.masterIdentifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>Identificador del documento</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -744,7 +744,7 @@
     <t>DocumentReference.status</t>
   </si>
   <si>
-    <t>current | superseded | entered-in-error</t>
+    <t>current: documento vigente</t>
   </si>
   <si>
     <t>The status of this document reference.</t>
@@ -808,7 +808,7 @@
     <t>DocumentReference.type</t>
   </si>
   <si>
-    <t>Kind of document (LOINC if possible)</t>
+    <t>Tipo de documento: LOINC 59258-4 (resumen de alta de urgencia)</t>
   </si>
   <si>
     <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
@@ -897,7 +897,7 @@
 </t>
   </si>
   <si>
-    <t>Who/what is the subject of the document</t>
+    <t>Paciente</t>
   </si>
   <si>
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
@@ -935,7 +935,7 @@
 </t>
   </si>
   <si>
-    <t>When this document reference was created</t>
+    <t>Fecha y hora de emisión del documento</t>
   </si>
   <si>
     <t>When the document reference was created.</t>
@@ -963,7 +963,7 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what authored the document</t>
+    <t>Profesional o establecimiento autor</t>
   </si>
   <si>
     <t>Identifies who is responsible for adding the information to the document.</t>
@@ -1031,7 +1031,7 @@
 </t>
   </si>
   <si>
-    <t>Organization which maintains the document</t>
+    <t>Establecimiento que custodia el documento</t>
   </si>
   <si>
     <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
@@ -1207,7 +1207,7 @@
     <t>DocumentReference.content</t>
   </si>
   <si>
-    <t>Document referenced</t>
+    <t>Contenido del documento</t>
   </si>
   <si>
     <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
@@ -1264,7 +1264,7 @@
     <t>DocumentReference.content.attachment.contentType</t>
   </si>
   <si>
-    <t>Mime type of the content, with charset etc.</t>
+    <t>Tipo MIME: application/pdf</t>
   </si>
   <si>
     <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
@@ -1423,7 +1423,7 @@
     <t>DocumentReference.content.attachment.title</t>
   </si>
   <si>
-    <t>Label to display in place of the data</t>
+    <t>Nombre del documento</t>
   </si>
   <si>
     <t>A label or set of text to display in place of the data.</t>
@@ -1448,7 +1448,7 @@
 </t>
   </si>
   <si>
-    <t>Date attachment was first created</t>
+    <t>Fecha de creación del PDF</t>
   </si>
   <si>
     <t>The date that the attachment was first created.</t>
@@ -1494,7 +1494,7 @@
     <t>DocumentReference.context</t>
   </si>
   <si>
-    <t>Clinical context of document</t>
+    <t>Contexto clínico del documento</t>
   </si>
   <si>
     <t>The clinical context in which the document was prepared.</t>
@@ -1518,11 +1518,11 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/encuentro-urgencia)
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/encuentro-urgencia)
 </t>
   </si>
   <si>
-    <t>Context of the document  content</t>
+    <t>Episodio de urgencia</t>
   </si>
   <si>
     <t>Describes the clinical encounter or type of care that the document content is associated with.</t>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-documento-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-documento-urgencia.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2846" uniqueCount="571">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,13 +341,190 @@
 </t>
   </si>
   <si>
-    <t>DocumentReference.implicitRules</t>
+    <t>DocumentReference.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>R (restringido) si el episodio está restringido</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>DocumentReference.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -443,28 +620,10 @@
     <t>DocumentReference.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>DocumentReference.modifierExtension</t>
@@ -526,39 +685,7 @@
     <t>DocumentReference.masterIdentifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DocumentReference.masterIdentifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>DocumentReference.masterIdentifier.use</t>
@@ -610,9 +737,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -808,7 +932,7 @@
     <t>DocumentReference.type</t>
   </si>
   <si>
-    <t>Tipo de documento: LOINC 59258-4 (resumen de alta de urgencia)</t>
+    <t>LOINC 59258-4 (resumen de alta de urgencia) en el alta | 34111-5 (nota de urgencia) en el abandono</t>
   </si>
   <si>
     <t>Specifies the particular kind of document referenced  (e.g. History and Physical, Discharge Summary, Progress Note). This usually equates to the purpose of making the document referenced.</t>
@@ -817,18 +941,7 @@
     <t>Key metadata element describing the document that describes he exact type of document. Helps humans to assess whether the document is of interest when viewing a list of documents.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="59258-4"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Precise type of clinical document.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes|4.0.1</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-tipo-documento-urgencia</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -869,9 +982,6 @@
     <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
@@ -931,10 +1041,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>Fecha y hora de emisión del documento</t>
   </si>
   <si>
@@ -1181,12 +1287,6 @@
   </si>
   <si>
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -1461,10 +1561,6 @@
   </si>
   <si>
     <t>DocumentReference.content.format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Format/content rules for the document</t>
@@ -2001,7 +2097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ64"/>
+  <dimension ref="A1:AQ72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.796875" customWidth="true" bestFit="true"/>
@@ -2029,7 +2125,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.4375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2568,10 +2664,10 @@
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>107</v>
@@ -2582,9 +2678,7 @@
       <c r="M5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>80</v>
@@ -2633,28 +2727,28 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM5" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>80</v>
@@ -2678,14 +2772,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -2697,16 +2791,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2732,43 +2826,43 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -2777,7 +2871,7 @@
         <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>80</v>
@@ -2794,14 +2888,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2817,10 +2911,10 @@
         <v>80</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>124</v>
@@ -2900,7 +2994,7 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>80</v>
@@ -2917,21 +3011,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>80</v>
@@ -2940,19 +3034,19 @@
         <v>80</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3002,19 +3096,19 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
@@ -3023,7 +3117,7 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>80</v>
@@ -3040,21 +3134,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>80</v>
@@ -3063,19 +3157,19 @@
         <v>80</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3125,19 +3219,19 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -3146,7 +3240,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
@@ -3163,14 +3257,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3183,26 +3277,24 @@
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -3250,7 +3342,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3262,7 +3354,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3271,7 +3363,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -3288,10 +3380,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3299,10 +3391,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>94</v>
@@ -3314,20 +3406,18 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
       </c>
@@ -3351,13 +3441,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3375,13 +3465,13 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>80</v>
@@ -3390,33 +3480,33 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3427,7 +3517,7 @@
         <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>80</v>
@@ -3436,18 +3526,20 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -3472,13 +3564,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3496,19 +3588,19 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3517,7 +3609,7 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
@@ -3534,42 +3626,42 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3607,31 +3699,31 @@
         <v>80</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>80</v>
@@ -3640,7 +3732,7 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
@@ -3657,10 +3749,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3677,26 +3769,24 @@
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -3720,13 +3810,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3744,7 +3834,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3765,7 +3855,7 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>80</v>
@@ -3774,7 +3864,7 @@
         <v>80</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>80</v>
@@ -3782,14 +3872,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3805,23 +3895,21 @@
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
       </c>
@@ -3845,13 +3933,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3869,7 +3957,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3899,54 +3987,52 @@
         <v>80</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>195</v>
+        <v>80</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3958,7 +4044,7 @@
         <v>80</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>80</v>
@@ -3994,19 +4080,19 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
@@ -4015,7 +4101,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -4024,50 +4110,50 @@
         <v>80</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4081,7 +4167,7 @@
         <v>80</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>80</v>
@@ -4117,19 +4203,19 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -4138,7 +4224,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -4147,7 +4233,7 @@
         <v>80</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>212</v>
+        <v>80</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>80</v>
@@ -4155,42 +4241,46 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -4238,19 +4328,19 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -4259,7 +4349,7 @@
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
@@ -4268,18 +4358,18 @@
         <v>80</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>80</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4287,13 +4377,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4302,18 +4392,20 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4361,7 +4453,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4376,33 +4468,33 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>80</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4413,7 +4505,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -4422,16 +4514,16 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>108</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>109</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4482,80 +4574,80 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>233</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>117</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4566,7 +4658,7 @@
         <v>80</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>80</v>
@@ -4581,72 +4673,72 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>239</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4663,24 +4755,26 @@
         <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4704,13 +4798,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4728,7 +4822,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4746,30 +4840,30 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>243</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4777,13 +4871,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
@@ -4792,18 +4886,20 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4812,7 +4908,7 @@
         <v>80</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>80</v>
@@ -4827,13 +4923,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4851,7 +4947,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4866,47 +4962,47 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>268</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4915,18 +5011,20 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -4938,7 +5036,7 @@
         <v>80</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>80</v>
+        <v>241</v>
       </c>
       <c r="U24" t="s" s="2">
         <v>80</v>
@@ -4950,13 +5048,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4974,13 +5072,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4992,30 +5090,30 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5038,15 +5136,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5059,7 +5159,7 @@
         <v>80</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>80</v>
@@ -5095,7 +5195,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5110,47 +5210,47 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>286</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>291</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
@@ -5159,17 +5259,15 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5218,7 +5316,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5233,33 +5331,33 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>299</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>301</v>
+        <v>80</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>302</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5267,13 +5365,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
@@ -5282,16 +5380,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5341,13 +5439,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
@@ -5356,33 +5454,33 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>307</v>
+        <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>310</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>311</v>
+        <v>267</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5393,7 +5491,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -5402,20 +5500,18 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>314</v>
+        <v>202</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5464,13 +5560,13 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
@@ -5479,33 +5575,33 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>307</v>
+        <v>207</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>321</v>
+        <v>211</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>322</v>
+        <v>272</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>323</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5522,22 +5618,22 @@
         <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>325</v>
+        <v>169</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5548,7 +5644,7 @@
         <v>80</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>80</v>
@@ -5563,13 +5659,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5587,10 +5683,10 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>93</v>
@@ -5602,33 +5698,33 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5639,7 +5735,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -5651,16 +5747,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>332</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5686,13 +5782,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5710,13 +5806,13 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
@@ -5728,30 +5824,30 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>336</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5759,30 +5855,32 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5807,13 +5905,11 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5831,7 +5927,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>167</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5843,40 +5939,40 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>168</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>138</v>
+        <v>308</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5892,19 +5988,19 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>170</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>142</v>
+        <v>311</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5930,13 +6026,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5954,7 +6050,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5966,72 +6062,68 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>168</v>
+        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -6079,52 +6171,52 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>136</v>
+        <v>324</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>80</v>
+        <v>326</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6134,7 +6226,7 @@
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
@@ -6143,16 +6235,16 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6178,13 +6270,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6202,10 +6294,10 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>93</v>
@@ -6217,33 +6309,33 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>354</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6254,10 +6346,10 @@
         <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
@@ -6266,15 +6358,17 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6323,13 +6417,13 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
@@ -6338,33 +6432,33 @@
         <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6384,23 +6478,21 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>164</v>
+        <v>350</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6448,7 +6540,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6463,33 +6555,33 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6497,35 +6589,33 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>186</v>
+        <v>361</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6549,13 +6639,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>375</v>
+        <v>80</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>376</v>
+        <v>80</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6573,13 +6663,13 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
@@ -6588,33 +6678,33 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6622,13 +6712,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>80</v>
@@ -6637,15 +6727,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6694,10 +6786,10 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>82</v>
@@ -6712,10 +6804,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6727,15 +6819,15 @@
         <v>80</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6758,13 +6850,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6815,7 +6907,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6836,7 +6928,7 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6853,14 +6945,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6879,16 +6971,16 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6938,7 +7030,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6950,7 +7042,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6959,7 +7051,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6976,14 +7068,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7002,19 +7094,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7063,7 +7155,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7075,7 +7167,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7084,7 +7176,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7101,10 +7193,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7127,15 +7219,17 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>391</v>
+        <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7160,13 +7254,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>80</v>
+        <v>386</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>80</v>
+        <v>387</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -7184,7 +7278,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7202,30 +7296,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7233,7 +7327,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -7245,16 +7339,16 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>164</v>
+        <v>392</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>393</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7305,10 +7399,10 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>167</v>
+        <v>391</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -7317,16 +7411,16 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7338,26 +7432,26 @@
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -7366,21 +7460,23 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>140</v>
+        <v>399</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>170</v>
+        <v>400</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7416,31 +7512,31 @@
         <v>80</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7449,7 +7545,7 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>168</v>
+        <v>403</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7458,18 +7554,18 @@
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>80</v>
+        <v>404</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7477,13 +7573,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>80</v>
@@ -7492,17 +7588,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>113</v>
+        <v>227</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7512,10 +7610,10 @@
         <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>405</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7527,37 +7625,37 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>80</v>
@@ -7569,30 +7667,30 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>80</v>
+        <v>415</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7600,13 +7698,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>80</v>
@@ -7615,18 +7713,16 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>113</v>
+        <v>368</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>414</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7638,7 +7734,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7650,13 +7746,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7677,10 +7773,10 @@
         <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
@@ -7692,10 +7788,10 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7712,10 +7808,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7738,20 +7834,16 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>420</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7799,7 +7891,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>110</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7811,7 +7903,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7820,7 +7912,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>425</v>
+        <v>111</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7829,54 +7921,52 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>426</v>
+        <v>80</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>428</v>
+        <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>115</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>430</v>
+        <v>116</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7888,7 +7978,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7924,19 +8014,19 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>434</v>
+        <v>121</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7945,7 +8035,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>435</v>
+        <v>111</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7954,7 +8044,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>436</v>
+        <v>80</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7962,45 +8052,45 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>438</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>117</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>199</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8049,19 +8139,19 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -8070,7 +8160,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>444</v>
+        <v>192</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8087,10 +8177,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8098,7 +8188,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8113,20 +8203,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -8174,10 +8260,10 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>93</v>
@@ -8192,30 +8278,30 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>428</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8229,27 +8315,25 @@
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>108</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>454</v>
+        <v>109</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>455</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8261,7 +8345,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>456</v>
+        <v>80</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8297,7 +8381,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>110</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8309,7 +8393,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8318,7 +8402,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>458</v>
+        <v>111</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8333,46 +8417,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>460</v>
+        <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>115</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8408,31 +8492,31 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>464</v>
+        <v>121</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -8441,7 +8525,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>444</v>
+        <v>111</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8456,12 +8540,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8469,13 +8553,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
@@ -8484,18 +8568,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>169</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8504,10 +8588,10 @@
         <v>80</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -8519,13 +8603,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>117</v>
+        <v>221</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8543,7 +8627,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8561,30 +8645,30 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>474</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8592,13 +8676,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
@@ -8607,18 +8691,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>332</v>
+        <v>169</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -8630,7 +8714,7 @@
         <v>80</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>80</v>
@@ -8642,13 +8726,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8666,7 +8750,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8687,7 +8771,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8704,10 +8788,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8730,16 +8814,20 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>164</v>
+        <v>453</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>165</v>
+        <v>454</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -8787,7 +8875,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>167</v>
+        <v>458</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8799,7 +8887,7 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -8808,7 +8896,7 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>168</v>
+        <v>459</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8817,52 +8905,54 @@
         <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>462</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>140</v>
+        <v>463</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>170</v>
+        <v>464</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8874,7 +8964,7 @@
         <v>80</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>80</v>
@@ -8910,19 +9000,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>174</v>
+        <v>468</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8931,7 +9021,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>168</v>
+        <v>469</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -8940,7 +9030,7 @@
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>80</v>
@@ -8948,45 +9038,45 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>472</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>343</v>
+        <v>473</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>344</v>
+        <v>474</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>142</v>
+        <v>475</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>148</v>
+        <v>476</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9035,19 +9125,19 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>345</v>
+        <v>477</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9056,7 +9146,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>136</v>
+        <v>478</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9071,12 +9161,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9084,31 +9174,35 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -9156,13 +9250,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -9171,19 +9265,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>487</v>
+        <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>488</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9192,12 +9286,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9208,30 +9302,30 @@
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9243,7 +9337,7 @@
         <v>80</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>80</v>
@@ -9255,13 +9349,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9285,7 +9379,7 @@
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -9297,10 +9391,10 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>497</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9312,15 +9406,15 @@
         <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>499</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9334,7 +9428,7 @@
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>80</v>
@@ -9343,16 +9437,18 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>214</v>
+        <v>494</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9400,7 +9496,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9418,13 +9514,13 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>503</v>
+        <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>504</v>
+        <v>478</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>505</v>
+        <v>80</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9433,15 +9529,15 @@
         <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>506</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9461,18 +9557,20 @@
         <v>80</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9497,13 +9595,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9521,7 +9619,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9539,13 +9637,13 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>513</v>
+        <v>420</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9554,15 +9652,15 @@
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9570,35 +9668,33 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>186</v>
+        <v>368</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9622,13 +9718,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>522</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9646,7 +9742,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9664,13 +9760,13 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>512</v>
+        <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9679,15 +9775,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>523</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9710,13 +9806,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>525</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>526</v>
+        <v>108</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>527</v>
+        <v>109</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9767,7 +9863,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>524</v>
+        <v>110</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9779,19 +9875,19 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>286</v>
+        <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>287</v>
+        <v>111</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9800,19 +9896,19 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9831,16 +9927,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>530</v>
+        <v>114</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>531</v>
+        <v>115</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>532</v>
+        <v>116</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>533</v>
+        <v>117</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9890,7 +9986,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>529</v>
+        <v>121</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9902,32 +9998,1012 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AK66" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
+      <c r="AM68" t="s" s="2">
         <v>537</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ64">
+  <autoFilter ref="A1:AQ72">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9937,7 +11013,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
